--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_ADJR2.xlsx
@@ -1,208 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.natif\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV0_ADJR2</t>
-  </si>
-  <si>
-    <t>LV1_ADJR2</t>
-  </si>
-  <si>
-    <t>LV2_ADJR2</t>
-  </si>
-  <si>
-    <t>LV3_ADJR2</t>
-  </si>
-  <si>
-    <t>LV4_ADJR2</t>
-  </si>
-  <si>
-    <t>LV5_ADJR2</t>
-  </si>
-  <si>
-    <t>LV6_ADJR2</t>
-  </si>
-  <si>
-    <t>LV7_ADJR2</t>
-  </si>
-  <si>
-    <t>LV8_ADJR2</t>
-  </si>
-  <si>
-    <t>LV9_ADJR2</t>
-  </si>
-  <si>
-    <t>LV10_ADJR2</t>
-  </si>
-  <si>
-    <t>LV11_ADJR2</t>
-  </si>
-  <si>
-    <t>LV12_ADJR2</t>
-  </si>
-  <si>
-    <t>LV13_ADJR2</t>
-  </si>
-  <si>
-    <t>LV14_ADJR2</t>
-  </si>
-  <si>
-    <t>LV15_ADJR2</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -235,80 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -350,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -382,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -417,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -593,2306 +350,2408 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_ADJR2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_ADJR2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_ADJR2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_ADJR2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_ADJR2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_ADJR2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_ADJR2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_ADJR2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_ADJR2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_ADJR2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_ADJR2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_ADJR2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_ADJR2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_ADJR2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_ADJR2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_ADJR2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C2">
-        <v>-5.0760306089323887E-2</v>
+        <v>-0.05076031130678652</v>
       </c>
       <c r="D2">
-        <v>-9.1199064325587512E-2</v>
+        <v>-0.09119910407022157</v>
       </c>
       <c r="E2">
-        <v>-8.3781990948968196E-2</v>
+        <v>-0.08378202738715028</v>
       </c>
       <c r="F2">
-        <v>-6.8682454430213993E-2</v>
+        <v>-0.06868247891277592</v>
       </c>
       <c r="G2">
-        <v>-8.919582588805719E-2</v>
+        <v>-0.08919591996232054</v>
       </c>
       <c r="H2">
-        <v>-8.6743055952972409E-2</v>
+        <v>-0.08674307154172758</v>
       </c>
       <c r="I2">
-        <v>-3.5100054229948392E-2</v>
+        <v>-0.03510005627166625</v>
       </c>
       <c r="J2">
-        <v>1.544401461511313E-2</v>
+        <v>0.01544401609578691</v>
       </c>
       <c r="K2">
-        <v>-1.6114726880386239E-2</v>
+        <v>-0.01611472066198792</v>
       </c>
       <c r="L2">
-        <v>3.618413635364133E-2</v>
+        <v>0.0361841435024223</v>
       </c>
       <c r="M2">
-        <v>0.1202218867928027</v>
+        <v>0.1202219325434644</v>
       </c>
       <c r="N2">
-        <v>0.1462236216641154</v>
+        <v>0.1462236062551365</v>
       </c>
       <c r="O2">
-        <v>0.25914419563070012</v>
-      </c>
-      <c r="P2" s="2">
-        <v>0.34115933308270158</v>
+        <v>0.2591441752030563</v>
+      </c>
+      <c r="P2">
+        <v>0.3411593281152018</v>
       </c>
       <c r="Q2">
-        <v>0.3832416408084291</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
+        <v>0.3832416380319545</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C3">
-        <v>-2.1784703184047419E-2</v>
+        <v>-0.02178471134524407</v>
       </c>
       <c r="D3">
-        <v>-0.1836540058058049</v>
+        <v>-0.1836540694687744</v>
       </c>
       <c r="E3">
-        <v>-0.13080340504963039</v>
+        <v>-0.1308034021030517</v>
       </c>
       <c r="F3">
-        <v>2.2779653551206459E-2</v>
+        <v>0.02277961312049607</v>
       </c>
       <c r="G3">
-        <v>9.9814043509296402E-2</v>
+        <v>0.09981402132878878</v>
       </c>
       <c r="H3">
-        <v>0.14890806285852029</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0.20945493222362879</v>
+        <v>0.1489081561270972</v>
+      </c>
+      <c r="I3">
+        <v>0.2094548857395022</v>
       </c>
       <c r="J3">
-        <v>0.23082796084211499</v>
+        <v>0.2308279773184552</v>
       </c>
       <c r="K3">
-        <v>0.2709599888605983</v>
+        <v>0.2709600322062766</v>
       </c>
       <c r="L3">
-        <v>0.31275846893664377</v>
+        <v>0.312758531699952</v>
       </c>
       <c r="M3">
-        <v>0.3061181032346651</v>
+        <v>0.3061181896023805</v>
       </c>
       <c r="N3">
-        <v>0.30544591984012121</v>
+        <v>0.3054460575534804</v>
       </c>
       <c r="O3">
-        <v>0.28323435450442691</v>
+        <v>0.2832346340108286</v>
       </c>
       <c r="P3">
-        <v>0.27093730987138182</v>
+        <v>0.2709376849810659</v>
       </c>
       <c r="Q3">
-        <v>0.28719961836556468</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
+        <v>0.2872000818682791</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C4">
-        <v>-4.5551217912491809E-2</v>
+        <v>-0.04555122059314672</v>
       </c>
       <c r="D4">
-        <v>-7.0146657080181113E-2</v>
+        <v>-0.07014677940014936</v>
       </c>
       <c r="E4">
-        <v>-0.14142584219960491</v>
+        <v>-0.1414258459722587</v>
       </c>
       <c r="F4">
-        <v>-0.14367005653628859</v>
+        <v>-0.1436700671083044</v>
       </c>
       <c r="G4">
-        <v>-0.20495449082784689</v>
+        <v>-0.2049544601088218</v>
       </c>
       <c r="H4">
-        <v>-8.9073540246515565E-2</v>
+        <v>-0.08907345294220544</v>
       </c>
       <c r="I4">
-        <v>-4.692850978129961E-4</v>
+        <v>-0.0004689389364024624</v>
       </c>
       <c r="J4">
-        <v>4.6372998811732798E-2</v>
+        <v>0.04637293416936498</v>
       </c>
       <c r="K4">
-        <v>5.1537844185087632E-2</v>
+        <v>0.05153792992659312</v>
       </c>
       <c r="L4">
-        <v>0.1276897223456776</v>
-      </c>
-      <c r="M4" s="2">
-        <v>0.20358189163539989</v>
+        <v>0.1276899823773735</v>
+      </c>
+      <c r="M4">
+        <v>0.2035818681414195</v>
       </c>
       <c r="N4">
-        <v>0.26545666612773833</v>
+        <v>0.2654566935620468</v>
       </c>
       <c r="O4">
-        <v>0.29776492893527079</v>
+        <v>0.2977649467279009</v>
       </c>
       <c r="P4">
-        <v>0.30216416809106589</v>
+        <v>0.3021641836159372</v>
       </c>
       <c r="Q4">
-        <v>0.28056876310679091</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
+        <v>0.280568779061452</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C5">
-        <v>-3.6885823473918583E-2</v>
+        <v>-0.03688583615657137</v>
       </c>
       <c r="D5">
-        <v>-0.1053811149014181</v>
+        <v>-0.1053811517810737</v>
       </c>
       <c r="E5">
-        <v>-5.7751621718993493E-2</v>
+        <v>-0.05775159737019993</v>
       </c>
       <c r="F5">
-        <v>-0.15253663812937851</v>
+        <v>-0.1525367970467095</v>
       </c>
       <c r="G5">
-        <v>5.5014642971173519E-2</v>
+        <v>0.0550145910002474</v>
       </c>
       <c r="H5">
-        <v>0.1380503622450015</v>
+        <v>0.1380503557247159</v>
       </c>
       <c r="I5">
-        <v>0.18631514700992119</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0.26091803691187743</v>
+        <v>0.1863151688074136</v>
+      </c>
+      <c r="J5">
+        <v>0.2609180424343685</v>
       </c>
       <c r="K5">
-        <v>0.32834674862810759</v>
+        <v>0.328346792116435</v>
       </c>
       <c r="L5">
-        <v>0.35702876197566491</v>
+        <v>0.3570288927382448</v>
       </c>
       <c r="M5">
-        <v>0.38824581599612512</v>
+        <v>0.3882458769483225</v>
       </c>
       <c r="N5">
-        <v>0.3902592390644728</v>
+        <v>0.3902593253473855</v>
       </c>
       <c r="O5">
-        <v>0.36721647945261332</v>
+        <v>0.3672165953114615</v>
       </c>
       <c r="P5">
-        <v>0.34517765789021188</v>
+        <v>0.3451777974538147</v>
       </c>
       <c r="Q5">
-        <v>0.32171564910436518</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
+        <v>0.3217158288336096</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C6">
-        <v>-3.3458454857208338E-2</v>
+        <v>-0.03345846395968876</v>
       </c>
       <c r="D6">
-        <v>-0.12645877462694899</v>
+        <v>-0.1264588410844752</v>
       </c>
       <c r="E6">
-        <v>-8.3177340287981322E-2</v>
+        <v>-0.08317732440845828</v>
       </c>
       <c r="F6">
-        <v>-0.11424673681383481</v>
+        <v>-0.1142467741605254</v>
       </c>
       <c r="G6">
-        <v>0.10614675802936439</v>
+        <v>0.1061466720631271</v>
       </c>
       <c r="H6">
-        <v>0.20708049094883191</v>
+        <v>0.2070805067623708</v>
       </c>
       <c r="I6">
-        <v>0.25395050616047349</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0.33604012061313132</v>
+        <v>0.2539504855122488</v>
+      </c>
+      <c r="J6">
+        <v>0.3360401556214012</v>
       </c>
       <c r="K6">
-        <v>0.37426636059640039</v>
+        <v>0.3742664541785496</v>
       </c>
       <c r="L6">
-        <v>0.38880005145138807</v>
+        <v>0.388799965865301</v>
       </c>
       <c r="M6">
-        <v>0.40920128587936261</v>
+        <v>0.4092013099959462</v>
       </c>
       <c r="N6">
-        <v>0.41478442620314743</v>
+        <v>0.4147844561752051</v>
       </c>
       <c r="O6">
-        <v>0.40805496869326441</v>
+        <v>0.408054994505808</v>
       </c>
       <c r="P6">
-        <v>0.41333752113135519</v>
+        <v>0.4133375739369484</v>
       </c>
       <c r="Q6">
-        <v>0.39040734243706432</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
+        <v>0.3904074023424604</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C7">
-        <v>-4.8179409482328628E-2</v>
+        <v>-0.048179413101557</v>
       </c>
       <c r="D7">
-        <v>-7.6567544327607887E-2</v>
+        <v>-0.07656755375720069</v>
       </c>
       <c r="E7">
-        <v>-0.1484933157258308</v>
+        <v>-0.1484932910386101</v>
       </c>
       <c r="F7">
-        <v>-0.1711848788498227</v>
+        <v>-0.1711849132920225</v>
       </c>
       <c r="G7">
-        <v>-0.2361387463398657</v>
+        <v>-0.2361387475062896</v>
       </c>
       <c r="H7">
-        <v>-0.18776839703561499</v>
+        <v>-0.1877682128132857</v>
       </c>
       <c r="I7">
-        <v>-7.5852357566519854E-2</v>
+        <v>-0.0758523342399581</v>
       </c>
       <c r="J7">
-        <v>2.3359720903310011E-2</v>
+        <v>0.02335975313538106</v>
       </c>
       <c r="K7">
-        <v>3.9868599231492413E-2</v>
+        <v>0.03986859680172371</v>
       </c>
       <c r="L7">
-        <v>6.6027888741920962E-2</v>
+        <v>0.06602784334023967</v>
       </c>
       <c r="M7">
-        <v>0.17350668858813059</v>
-      </c>
-      <c r="N7" s="2">
-        <v>0.25016054000684329</v>
+        <v>0.1735066741819719</v>
+      </c>
+      <c r="N7">
+        <v>0.2501605686710683</v>
       </c>
       <c r="O7">
-        <v>0.3035423551825</v>
+        <v>0.3035423687752864</v>
       </c>
       <c r="P7">
-        <v>0.33041086411890852</v>
+        <v>0.3304108729196816</v>
       </c>
       <c r="Q7">
-        <v>0.33374440533471522</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
+        <v>0.3337444154113471</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C8">
-        <v>-4.2865679853720737E-2</v>
+        <v>-0.04286568047849462</v>
       </c>
       <c r="D8">
-        <v>-7.3799612970461254E-2</v>
+        <v>-0.07379962732791183</v>
       </c>
       <c r="E8">
-        <v>-0.13783896918590949</v>
+        <v>-0.1378390736925912</v>
       </c>
       <c r="F8">
-        <v>-0.1746833431637427</v>
+        <v>-0.1746832963917096</v>
       </c>
       <c r="G8">
-        <v>-0.12620351785038469</v>
+        <v>-0.1262035173038347</v>
       </c>
       <c r="H8">
-        <v>-1.4728649980512791E-2</v>
+        <v>-0.01472860143950269</v>
       </c>
       <c r="I8">
-        <v>-4.1507982933785721E-3</v>
+        <v>-0.004150794319792348</v>
       </c>
       <c r="J8">
-        <v>0.101125755317307</v>
+        <v>0.1011258062668597</v>
       </c>
       <c r="K8">
-        <v>0.14340464876690581</v>
-      </c>
-      <c r="L8" s="2">
-        <v>0.26538554932171998</v>
+        <v>0.1434047189240129</v>
+      </c>
+      <c r="L8">
+        <v>0.2653855987848341</v>
       </c>
       <c r="M8">
-        <v>0.2755446472300821</v>
+        <v>0.275544686457985</v>
       </c>
       <c r="N8">
-        <v>0.32320003597498093</v>
+        <v>0.3232000534984331</v>
       </c>
       <c r="O8">
-        <v>0.34222753224146252</v>
+        <v>0.3422275433838365</v>
       </c>
       <c r="P8">
-        <v>0.34372223412262243</v>
+        <v>0.3437222366699295</v>
       </c>
       <c r="Q8">
-        <v>0.32927516990087419</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
+        <v>0.3292751816179179</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C9">
-        <v>-4.0532279859009368E-2</v>
+        <v>-0.04053228221132635</v>
       </c>
       <c r="D9">
-        <v>-6.8895938680059804E-2</v>
+        <v>-0.06889599334285849</v>
       </c>
       <c r="E9">
-        <v>-0.14281488912923121</v>
+        <v>-0.1428148907986295</v>
       </c>
       <c r="F9">
-        <v>-0.17352003752120559</v>
+        <v>-0.1735199590993766</v>
       </c>
       <c r="G9">
-        <v>-0.1181331106805579</v>
+        <v>-0.1181331095329005</v>
       </c>
       <c r="H9">
-        <v>-1.0578793502869071E-2</v>
+        <v>-0.01057893150496146</v>
       </c>
       <c r="I9">
-        <v>-5.4730212525314426E-3</v>
+        <v>-0.005472969715074222</v>
       </c>
       <c r="J9">
-        <v>0.1009658819289611</v>
+        <v>0.1009658787855461</v>
       </c>
       <c r="K9">
-        <v>0.12827336174814291</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0.28433867176451427</v>
+        <v>0.1282734336820326</v>
+      </c>
+      <c r="L9">
+        <v>0.2843386907135198</v>
       </c>
       <c r="M9">
-        <v>0.27488063480842528</v>
+        <v>0.2748806397181108</v>
       </c>
       <c r="N9">
-        <v>0.31536399250923858</v>
+        <v>0.3153639989953979</v>
       </c>
       <c r="O9">
-        <v>0.3445134290959857</v>
+        <v>0.3445134151713622</v>
       </c>
       <c r="P9">
-        <v>0.34659050556300403</v>
+        <v>0.3465904901074256</v>
       </c>
       <c r="Q9">
-        <v>0.34537125771537203</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
+        <v>0.3453712444492792</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C10">
-        <v>-3.881136347182599E-2</v>
+        <v>-0.03881136737268608</v>
       </c>
       <c r="D10">
-        <v>-6.4423724284543279E-2</v>
+        <v>-0.06442375132091155</v>
       </c>
       <c r="E10">
-        <v>-0.12925042684661461</v>
+        <v>-0.1292505603010121</v>
       </c>
       <c r="F10">
-        <v>-0.1502293249044046</v>
+        <v>-0.1502292379044779</v>
       </c>
       <c r="G10">
-        <v>-0.1023211666714192</v>
+        <v>-0.1023211546942787</v>
       </c>
       <c r="H10">
-        <v>2.3554811085064538E-3</v>
+        <v>0.002355504162136517</v>
       </c>
       <c r="I10">
-        <v>1.6001848581917329E-2</v>
+        <v>0.01600185330697554</v>
       </c>
       <c r="J10">
-        <v>0.1115938013566264</v>
+        <v>0.1115938540964191</v>
       </c>
       <c r="K10">
-        <v>0.13823641775081399</v>
-      </c>
-      <c r="L10" s="2">
-        <v>0.28559346025603188</v>
+        <v>0.1382364843463339</v>
+      </c>
+      <c r="L10">
+        <v>0.2855934656458675</v>
       </c>
       <c r="M10">
-        <v>0.27977382485151042</v>
+        <v>0.2797738246541456</v>
       </c>
       <c r="N10">
-        <v>0.32379828477001071</v>
+        <v>0.3237983020605837</v>
       </c>
       <c r="O10">
-        <v>0.3485492063317927</v>
+        <v>0.3485491961513864</v>
       </c>
       <c r="P10">
-        <v>0.34291843602730337</v>
+        <v>0.342918430478959</v>
       </c>
       <c r="Q10">
-        <v>0.33785971706853229</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
+        <v>0.3378597126077672</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C11">
-        <v>-4.366716713564147E-2</v>
+        <v>-0.04366716958034533</v>
       </c>
       <c r="D11">
-        <v>-7.0464926842110656E-2</v>
+        <v>-0.07046496636574538</v>
       </c>
       <c r="E11">
-        <v>-0.1376703375147274</v>
+        <v>-0.1376705689045609</v>
       </c>
       <c r="F11">
-        <v>-0.17100811484458439</v>
+        <v>-0.1710080717825602</v>
       </c>
       <c r="G11">
-        <v>-0.1193990904740922</v>
+        <v>-0.1193990989433337</v>
       </c>
       <c r="H11">
-        <v>-2.2204968788808718E-2</v>
+        <v>-0.02220493954320528</v>
       </c>
       <c r="I11">
-        <v>-1.5177226661513891E-2</v>
+        <v>-0.01517778038245859</v>
       </c>
       <c r="J11">
-        <v>8.2197821973780727E-2</v>
+        <v>0.08220947557190089</v>
       </c>
       <c r="K11">
-        <v>0.1146880110772161</v>
-      </c>
-      <c r="L11" s="2">
-        <v>0.27667597002335748</v>
+        <v>0.1146897261883449</v>
+      </c>
+      <c r="L11">
+        <v>0.2766759730821362</v>
       </c>
       <c r="M11">
-        <v>0.27990156185860021</v>
+        <v>0.2799015616527206</v>
       </c>
       <c r="N11">
-        <v>0.32280141611376839</v>
+        <v>0.3228014189117526</v>
       </c>
       <c r="O11">
-        <v>0.34709694575470512</v>
+        <v>0.3470969358853951</v>
       </c>
       <c r="P11">
-        <v>0.34555380593126528</v>
+        <v>0.3455537958401499</v>
       </c>
       <c r="Q11">
-        <v>0.34798449098414391</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
+        <v>0.3479844857826014</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C12">
-        <v>-3.2698252750561818E-2</v>
+        <v>-0.03269825953818891</v>
       </c>
       <c r="D12">
-        <v>-9.2550325827629176E-2</v>
+        <v>-0.09255035860301451</v>
       </c>
       <c r="E12">
-        <v>-5.1827024442805437E-2</v>
+        <v>-0.0518270206237492</v>
       </c>
       <c r="F12">
-        <v>-0.139847554582442</v>
+        <v>-0.1398475817642008</v>
       </c>
       <c r="G12">
-        <v>2.9967042679074879E-2</v>
+        <v>0.029967016823737</v>
       </c>
       <c r="H12">
-        <v>9.299508241695803E-2</v>
+        <v>0.09299505910719212</v>
       </c>
       <c r="I12">
-        <v>0.19649852697080869</v>
+        <v>0.1964985360577225</v>
       </c>
       <c r="J12">
-        <v>0.29763549864281308</v>
-      </c>
-      <c r="K12" s="2">
-        <v>0.35933573937250829</v>
+        <v>0.2976354859214426</v>
+      </c>
+      <c r="K12">
+        <v>0.3593357815591688</v>
       </c>
       <c r="L12">
-        <v>0.38824782060962348</v>
+        <v>0.388247898163165</v>
       </c>
       <c r="M12">
-        <v>0.41918248335403457</v>
+        <v>0.4191825818529463</v>
       </c>
       <c r="N12">
-        <v>0.42470336646426621</v>
+        <v>0.4247034626400178</v>
       </c>
       <c r="O12">
-        <v>0.40463831315297188</v>
+        <v>0.4046384236256988</v>
       </c>
       <c r="P12">
-        <v>0.38701211053077011</v>
+        <v>0.387012253870853</v>
       </c>
       <c r="Q12">
-        <v>0.35066707113517048</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
+        <v>0.3506672580542208</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C13">
-        <v>-4.4289665153054728E-2</v>
+        <v>-0.04428968187419952</v>
       </c>
       <c r="D13">
-        <v>-0.1817010365798159</v>
+        <v>-0.1817010746818999</v>
       </c>
       <c r="E13">
-        <v>-0.113025325762863</v>
+        <v>-0.1130253184257776</v>
       </c>
       <c r="F13">
-        <v>-0.161394035301375</v>
+        <v>-0.1613941362377644</v>
       </c>
       <c r="G13">
-        <v>-0.1591108403428787</v>
+        <v>-0.1591108888254304</v>
       </c>
       <c r="H13">
-        <v>-1.319739024232556E-2</v>
+        <v>-0.01319741800756877</v>
       </c>
       <c r="I13">
-        <v>-3.1407553632258321E-3</v>
+        <v>-0.003140806135033387</v>
       </c>
       <c r="J13">
-        <v>4.7578530694834052E-2</v>
+        <v>0.04757848698955097</v>
       </c>
       <c r="K13">
-        <v>0.12901632299170629</v>
-      </c>
-      <c r="L13" s="2">
-        <v>0.20478002844279</v>
+        <v>0.1290162967912749</v>
+      </c>
+      <c r="L13">
+        <v>0.2047800552649331</v>
       </c>
       <c r="M13">
-        <v>0.2181745254977846</v>
+        <v>0.2181745661183285</v>
       </c>
       <c r="N13">
-        <v>0.2436295714090608</v>
+        <v>0.2436296339105126</v>
       </c>
       <c r="O13">
-        <v>0.24536032016385351</v>
+        <v>0.2453604168687865</v>
       </c>
       <c r="P13">
-        <v>0.26801173258871891</v>
+        <v>0.2680118898954699</v>
       </c>
       <c r="Q13">
-        <v>0.25790170399893247</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>29</v>
+        <v>0.2579018894708019</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C14">
-        <v>-4.4941082695398787E-2</v>
+        <v>-0.04494108307508588</v>
       </c>
       <c r="D14">
-        <v>-7.0516358848907709E-2</v>
+        <v>-0.07051638559893003</v>
       </c>
       <c r="E14">
-        <v>-0.13956289655248169</v>
+        <v>-0.1395629028132194</v>
       </c>
       <c r="F14">
-        <v>-0.1638220760658626</v>
+        <v>-0.1638221682470258</v>
       </c>
       <c r="G14">
-        <v>-0.22107747327379379</v>
+        <v>-0.221077563327815</v>
       </c>
       <c r="H14">
-        <v>-0.17251964610350889</v>
+        <v>-0.1725195958347692</v>
       </c>
       <c r="I14">
-        <v>-6.7934558172047813E-2</v>
+        <v>-0.06793456645732829</v>
       </c>
       <c r="J14">
-        <v>2.121720329641617E-2</v>
+        <v>0.02121720231577748</v>
       </c>
       <c r="K14">
-        <v>5.1137525793332729E-2</v>
+        <v>0.0511375123127653</v>
       </c>
       <c r="L14">
-        <v>7.1829807608517926E-2</v>
+        <v>0.07182992098313833</v>
       </c>
       <c r="M14">
-        <v>0.18083751760259881</v>
-      </c>
-      <c r="N14" s="2">
-        <v>0.28875856947630679</v>
+        <v>0.1808373716830427</v>
+      </c>
+      <c r="N14">
+        <v>0.2887585642663168</v>
       </c>
       <c r="O14">
-        <v>0.32975530285487797</v>
+        <v>0.3297553018447872</v>
       </c>
       <c r="P14">
-        <v>0.35743453031196898</v>
+        <v>0.3574345324654836</v>
       </c>
       <c r="Q14">
-        <v>0.38041072501968359</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>30</v>
+        <v>0.3804107177665828</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C15">
-        <v>-4.1627696416332169E-2</v>
+        <v>-0.04162769852361812</v>
       </c>
       <c r="D15">
-        <v>-6.5622536011725158E-2</v>
+        <v>-0.06562256249431883</v>
       </c>
       <c r="E15">
-        <v>-0.1285622969038375</v>
+        <v>-0.1285623734863381</v>
       </c>
       <c r="F15">
-        <v>-0.14346655767922201</v>
+        <v>-0.1434665761616356</v>
       </c>
       <c r="G15">
-        <v>-0.19310627649916989</v>
+        <v>-0.1931062558763979</v>
       </c>
       <c r="H15">
-        <v>-0.15064894828310671</v>
+        <v>-0.15064879814574</v>
       </c>
       <c r="I15">
-        <v>-4.4061013989195409E-2</v>
+        <v>-0.04406095595134042</v>
       </c>
       <c r="J15">
-        <v>2.3678949656459568E-2</v>
+        <v>0.02367895678235256</v>
       </c>
       <c r="K15">
-        <v>5.4301471979794153E-2</v>
+        <v>0.05430146643439627</v>
       </c>
       <c r="L15">
-        <v>6.6875719593464042E-2</v>
+        <v>0.06687570736474341</v>
       </c>
       <c r="M15">
-        <v>0.16039490477855409</v>
-      </c>
-      <c r="N15" s="2">
-        <v>0.26492563194174018</v>
+        <v>0.1603949122436407</v>
+      </c>
+      <c r="N15">
+        <v>0.2649256241295233</v>
       </c>
       <c r="O15">
-        <v>0.30367351218477651</v>
+        <v>0.3036735055175696</v>
       </c>
       <c r="P15">
-        <v>0.32730218802155497</v>
+        <v>0.3273021795128061</v>
       </c>
       <c r="Q15">
-        <v>0.34639377755754092</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>31</v>
+        <v>0.34639376451494</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C16">
-        <v>-4.8659621993792958E-2</v>
+        <v>-0.04865962290637611</v>
       </c>
       <c r="D16">
-        <v>-7.5266989944081972E-2</v>
+        <v>-0.07526698999826453</v>
       </c>
       <c r="E16">
-        <v>-0.1395947013974955</v>
+        <v>-0.139594689867859</v>
       </c>
       <c r="F16">
-        <v>-0.1567609807903399</v>
+        <v>-0.1567609917808589</v>
       </c>
       <c r="G16">
-        <v>-0.21159874100949469</v>
+        <v>-0.211598693234716</v>
       </c>
       <c r="H16">
-        <v>-0.1659135775675725</v>
+        <v>-0.1659135032593476</v>
       </c>
       <c r="I16">
-        <v>-5.8494323700376098E-2</v>
+        <v>-0.05849430345742757</v>
       </c>
       <c r="J16">
-        <v>2.5575182192896961E-2</v>
+        <v>0.02557516873092323</v>
       </c>
       <c r="K16">
-        <v>4.5727510327543387E-2</v>
+        <v>0.04572752434994913</v>
       </c>
       <c r="L16">
-        <v>6.1648822174612178E-2</v>
+        <v>0.06164875977998125</v>
       </c>
       <c r="M16">
-        <v>0.15332715027264279</v>
-      </c>
-      <c r="N16" s="2">
-        <v>0.26114016964458459</v>
+        <v>0.1533272297021085</v>
+      </c>
+      <c r="N16">
+        <v>0.2611401933403639</v>
       </c>
       <c r="O16">
-        <v>0.30466088098539168</v>
+        <v>0.3046608777337101</v>
       </c>
       <c r="P16">
-        <v>0.33725627131746488</v>
+        <v>0.3372562706301454</v>
       </c>
       <c r="Q16">
-        <v>0.35849317911355111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
+        <v>0.3584931587381339</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C17">
-        <v>-4.3867541925287537E-2</v>
+        <v>-0.04386754462467502</v>
       </c>
       <c r="D17">
-        <v>-6.2440217216917213E-2</v>
+        <v>-0.06244024516302913</v>
       </c>
       <c r="E17">
-        <v>-0.12748287663450389</v>
+        <v>-0.1274828741140688</v>
       </c>
       <c r="F17">
-        <v>-0.14364474690088661</v>
+        <v>-0.1436447340038612</v>
       </c>
       <c r="G17">
-        <v>-0.20538544676058579</v>
+        <v>-0.2053854726819965</v>
       </c>
       <c r="H17">
-        <v>-0.16306792612764981</v>
+        <v>-0.1630681377148206</v>
       </c>
       <c r="I17">
-        <v>-6.577448443359242E-2</v>
+        <v>-0.0657744969681006</v>
       </c>
       <c r="J17">
-        <v>6.9879344634859574E-3</v>
+        <v>0.006987926077372716</v>
       </c>
       <c r="K17">
-        <v>4.1939314651794693E-2</v>
+        <v>0.04193931707660614</v>
       </c>
       <c r="L17">
-        <v>4.8595898675979479E-2</v>
+        <v>0.04859595819711695</v>
       </c>
       <c r="M17">
-        <v>0.13870225669820299</v>
-      </c>
-      <c r="N17" s="2">
-        <v>0.23727066899107649</v>
+        <v>0.1387037045326971</v>
+      </c>
+      <c r="N17">
+        <v>0.237272118685136</v>
       </c>
       <c r="O17">
-        <v>0.27737230732676832</v>
+        <v>0.2773722806849702</v>
       </c>
       <c r="P17">
-        <v>0.3065013182020716</v>
+        <v>0.306501327360693</v>
       </c>
       <c r="Q17">
-        <v>0.33745507773715178</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>33</v>
+        <v>0.3374550725017906</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C18">
-        <v>-3.4828627683201878E-2</v>
+        <v>-0.03482863514224802</v>
       </c>
       <c r="D18">
-        <v>-0.1045636705630829</v>
+        <v>-0.1045636701075621</v>
       </c>
       <c r="E18">
-        <v>-5.0418403695272757E-2</v>
+        <v>-0.0504183399542647</v>
       </c>
       <c r="F18">
-        <v>-0.1523259528739434</v>
+        <v>-0.1523259958394004</v>
       </c>
       <c r="G18">
-        <v>5.8053909062709609E-2</v>
+        <v>0.05805385245526924</v>
       </c>
       <c r="H18">
-        <v>0.12810909225448361</v>
+        <v>0.1281090709160203</v>
       </c>
       <c r="I18">
-        <v>0.20497934289865519</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0.29755671569032988</v>
+        <v>0.2049793561932502</v>
+      </c>
+      <c r="J18">
+        <v>0.2975567331064028</v>
       </c>
       <c r="K18">
-        <v>0.36682457826949938</v>
+        <v>0.3668246126812105</v>
       </c>
       <c r="L18">
-        <v>0.38262705951309961</v>
+        <v>0.3826271139604915</v>
       </c>
       <c r="M18">
-        <v>0.40882698703008602</v>
+        <v>0.4088270332876491</v>
       </c>
       <c r="N18">
-        <v>0.41362358920929748</v>
+        <v>0.4136236827032853</v>
       </c>
       <c r="O18">
-        <v>0.38564343722491878</v>
+        <v>0.3856435505511379</v>
       </c>
       <c r="P18">
-        <v>0.36559283100493561</v>
+        <v>0.3655929702953352</v>
       </c>
       <c r="Q18">
-        <v>0.34314902759993032</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>34</v>
+        <v>0.3431492069919129</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C19">
-        <v>-4.6012679597663621E-2</v>
+        <v>-0.04601270401513568</v>
       </c>
       <c r="D19">
-        <v>-0.14035944974364581</v>
+        <v>-0.1403594986117713</v>
       </c>
       <c r="E19">
-        <v>-9.8851422293065705E-2</v>
+        <v>-0.09885141824585275</v>
       </c>
       <c r="F19">
-        <v>-0.1345156227069467</v>
+        <v>-0.1345157162732133</v>
       </c>
       <c r="G19">
-        <v>0.11530534819230789</v>
+        <v>0.1153053303407343</v>
       </c>
       <c r="H19">
-        <v>0.20330690642922231</v>
+        <v>0.2033068718382776</v>
       </c>
       <c r="I19">
-        <v>0.261130302453916</v>
-      </c>
-      <c r="J19" s="4">
-        <v>0.34572791440842171</v>
+        <v>0.2611302862135575</v>
+      </c>
+      <c r="J19">
+        <v>0.3457279233617193</v>
       </c>
       <c r="K19">
-        <v>0.39615483170196408</v>
+        <v>0.3961548520137582</v>
       </c>
       <c r="L19">
-        <v>0.40888454225104831</v>
+        <v>0.4088845573537608</v>
       </c>
       <c r="M19">
-        <v>0.4358816083362711</v>
+        <v>0.4358816216043777</v>
       </c>
       <c r="N19">
-        <v>0.4327571423850296</v>
+        <v>0.4327571548068798</v>
       </c>
       <c r="O19">
-        <v>0.42092898557003489</v>
+        <v>0.4209289984516154</v>
       </c>
       <c r="P19">
-        <v>0.4278558933951514</v>
+        <v>0.4278559204351786</v>
       </c>
       <c r="Q19">
-        <v>0.41943105355089177</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
+        <v>0.4194311087286677</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C20">
-        <v>-3.8548549759861758E-2</v>
+        <v>-0.03854855218549918</v>
       </c>
       <c r="D20">
-        <v>-0.14832249787934559</v>
+        <v>-0.1483225682561313</v>
       </c>
       <c r="E20">
-        <v>-0.1083076597568321</v>
+        <v>-0.1083076653165454</v>
       </c>
       <c r="F20">
-        <v>-1.8583072622637382E-2</v>
+        <v>-0.01858298679673868</v>
       </c>
       <c r="G20">
-        <v>0.102225506552204</v>
+        <v>0.1022255300763224</v>
       </c>
       <c r="H20">
-        <v>0.1385090345044199</v>
+        <v>0.138509034105626</v>
       </c>
       <c r="I20">
-        <v>0.2370932521753743</v>
+        <v>0.2370932731396988</v>
       </c>
       <c r="J20">
-        <v>0.31220785456573558</v>
-      </c>
-      <c r="K20" s="2">
-        <v>0.34863602721189962</v>
+        <v>0.3122078925684028</v>
+      </c>
+      <c r="K20">
+        <v>0.3486360527713397</v>
       </c>
       <c r="L20">
-        <v>0.39737718327380211</v>
+        <v>0.3973772129950086</v>
       </c>
       <c r="M20">
-        <v>0.40040475349846938</v>
+        <v>0.4004047563266826</v>
       </c>
       <c r="N20">
-        <v>0.40594456119222289</v>
+        <v>0.4059445683663143</v>
       </c>
       <c r="O20">
-        <v>0.44241881584017978</v>
+        <v>0.4424188350467268</v>
       </c>
       <c r="P20">
-        <v>0.44463936349094241</v>
+        <v>0.4446394073060036</v>
       </c>
       <c r="Q20">
-        <v>0.44738082111383298</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>36</v>
+        <v>0.4473808687951081</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C21">
-        <v>-2.3986836621994918E-2</v>
+        <v>-0.02398684426476878</v>
       </c>
       <c r="D21">
-        <v>-0.1933722877724626</v>
+        <v>-0.1933723537924121</v>
       </c>
       <c r="E21">
-        <v>-0.13727698363590429</v>
+        <v>-0.1372769685160876</v>
       </c>
       <c r="F21">
-        <v>-1.146466511697769E-2</v>
+        <v>-0.01146473305673586</v>
       </c>
       <c r="G21">
-        <v>5.9077058142668858E-2</v>
+        <v>0.05907732132734889</v>
       </c>
       <c r="H21">
-        <v>9.0834699351538539E-2</v>
+        <v>0.09083472489086498</v>
       </c>
       <c r="I21">
-        <v>0.1418509080373957</v>
-      </c>
-      <c r="J21" s="2">
-        <v>0.19453542296391721</v>
+        <v>0.1418508146539647</v>
+      </c>
+      <c r="J21">
+        <v>0.1945354559018462</v>
       </c>
       <c r="K21">
-        <v>0.26453035875043929</v>
+        <v>0.2645304376595029</v>
       </c>
       <c r="L21">
-        <v>0.3007866804685666</v>
+        <v>0.3007867800968763</v>
       </c>
       <c r="M21">
-        <v>0.31412155688861032</v>
+        <v>0.3141217022694872</v>
       </c>
       <c r="N21">
-        <v>0.29967743713258022</v>
+        <v>0.2996776501270632</v>
       </c>
       <c r="O21">
-        <v>0.26077383937920562</v>
+        <v>0.2607741443760178</v>
       </c>
       <c r="P21">
-        <v>0.23765436570944981</v>
+        <v>0.2376547901802222</v>
       </c>
       <c r="Q21">
-        <v>0.24955042209503189</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>37</v>
+        <v>0.2495509114274926</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C22">
-        <v>-2.4607947014113399E-2</v>
+        <v>-0.02460795494820295</v>
       </c>
       <c r="D22">
-        <v>-0.18411424604785079</v>
+        <v>-0.184114318063784</v>
       </c>
       <c r="E22">
-        <v>-0.1290674248820759</v>
+        <v>-0.1290674363887027</v>
       </c>
       <c r="F22">
-        <v>-1.444957127082154E-3</v>
+        <v>-0.001444968446907617</v>
       </c>
       <c r="G22">
-        <v>5.1378181697079063E-2</v>
+        <v>0.0513781767324361</v>
       </c>
       <c r="H22">
-        <v>7.7234929345367298E-2</v>
+        <v>0.07723484809669987</v>
       </c>
       <c r="I22">
-        <v>0.1018220505065623</v>
+        <v>0.1018220873980269</v>
       </c>
       <c r="J22">
-        <v>0.1219006826227986</v>
-      </c>
-      <c r="K22" s="2">
-        <v>0.1955586688494432</v>
+        <v>0.1219007516360316</v>
+      </c>
+      <c r="K22">
+        <v>0.1955587851546902</v>
       </c>
       <c r="L22">
-        <v>0.23803099272159811</v>
+        <v>0.2380311269967776</v>
       </c>
       <c r="M22">
-        <v>0.26140724899842599</v>
+        <v>0.261407418663237</v>
       </c>
       <c r="N22">
-        <v>0.27256556506457358</v>
+        <v>0.2725658129654691</v>
       </c>
       <c r="O22">
-        <v>0.25481874645357638</v>
+        <v>0.2548191152038499</v>
       </c>
       <c r="P22">
-        <v>0.2479236019785501</v>
+        <v>0.2479240669882248</v>
       </c>
       <c r="Q22">
-        <v>0.24289508261368811</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>38</v>
+        <v>0.2428956329226711</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C23">
-        <v>-3.3966391673629658E-2</v>
+        <v>-0.03396642352283137</v>
       </c>
       <c r="D23">
-        <v>-0.1534015392222027</v>
+        <v>-0.1534014998751957</v>
       </c>
       <c r="E23">
-        <v>-3.6124300470172593E-2</v>
+        <v>-0.0361243485624908</v>
       </c>
       <c r="F23">
-        <v>7.3634047482709089E-2</v>
+        <v>0.07363412936455427</v>
       </c>
       <c r="G23">
-        <v>0.20798300500296521</v>
+        <v>0.207983173625593</v>
       </c>
       <c r="H23">
-        <v>0.29443301258018811</v>
+        <v>0.2944330197675165</v>
       </c>
       <c r="I23">
-        <v>0.32524747594897169</v>
-      </c>
-      <c r="J23" s="2">
-        <v>0.33875630482770203</v>
+        <v>0.3252474996601295</v>
+      </c>
+      <c r="J23">
+        <v>0.3387563640452737</v>
       </c>
       <c r="K23">
-        <v>0.36211836408806453</v>
+        <v>0.3621184769219276</v>
       </c>
       <c r="L23">
-        <v>0.36832104909139618</v>
+        <v>0.3683212818107829</v>
       </c>
       <c r="M23">
-        <v>0.36850020782208792</v>
+        <v>0.3685005201621628</v>
       </c>
       <c r="N23">
-        <v>0.35696910693012379</v>
+        <v>0.3569695248078881</v>
       </c>
       <c r="O23">
-        <v>0.3485159217783183</v>
+        <v>0.3485163961829496</v>
       </c>
       <c r="P23">
-        <v>0.35099532299303909</v>
+        <v>0.3509957993852315</v>
       </c>
       <c r="Q23">
-        <v>0.32862867708809612</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>39</v>
+        <v>0.3286291540874908</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C24">
-        <v>-7.1858544647608727E-2</v>
+        <v>-0.07185854699925386</v>
       </c>
       <c r="D24">
-        <v>-0.1328441396214928</v>
+        <v>-0.1328440943255675</v>
       </c>
       <c r="E24">
-        <v>-0.19259433769453591</v>
+        <v>-0.1925943555124475</v>
       </c>
       <c r="F24">
-        <v>-0.149493303370002</v>
+        <v>-0.1494932471594896</v>
       </c>
       <c r="G24">
-        <v>-0.13111711532549189</v>
+        <v>-0.1311170879183998</v>
       </c>
       <c r="H24">
-        <v>-7.6565447075566895E-2</v>
+        <v>-0.07656538942226108</v>
       </c>
       <c r="I24">
-        <v>-0.1190332419221726</v>
+        <v>-0.1190332407189242</v>
       </c>
       <c r="J24">
-        <v>-6.727013778044498E-2</v>
-      </c>
-      <c r="K24" s="2">
-        <v>9.3147234878773744E-2</v>
+        <v>-0.06727037363131398</v>
+      </c>
+      <c r="K24">
+        <v>0.09314721497116657</v>
       </c>
       <c r="L24">
-        <v>0.19011204258841211</v>
+        <v>0.1901121174027857</v>
       </c>
       <c r="M24">
-        <v>0.2191681014158311</v>
+        <v>0.2191682419369749</v>
       </c>
       <c r="N24">
-        <v>0.19842144357744901</v>
+        <v>0.1984217125411406</v>
       </c>
       <c r="O24">
-        <v>0.13490403418338581</v>
+        <v>0.1349044121800771</v>
       </c>
       <c r="P24">
-        <v>7.3851842915175797E-2</v>
+        <v>0.07385230372431485</v>
       </c>
       <c r="Q24">
-        <v>-9.9235247514425553E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>40</v>
+        <v>-0.009922935883072461</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C25">
-        <v>-6.9359185286404113E-2</v>
+        <v>-0.06935919506317464</v>
       </c>
       <c r="D25">
-        <v>-0.1275483732043034</v>
+        <v>-0.127548276724069</v>
       </c>
       <c r="E25">
-        <v>-0.1879707532806788</v>
+        <v>-0.1879707857626263</v>
       </c>
       <c r="F25">
-        <v>-0.13910606036587411</v>
+        <v>-0.1391060770682653</v>
       </c>
       <c r="G25">
-        <v>-0.11746465444103429</v>
+        <v>-0.1174646030066644</v>
       </c>
       <c r="H25">
-        <v>-0.10019322616698401</v>
+        <v>-0.1001932301528103</v>
       </c>
       <c r="I25">
-        <v>-0.20190270583851749</v>
+        <v>-0.2019026901174304</v>
       </c>
       <c r="J25">
-        <v>-0.14489780202162261</v>
+        <v>-0.1448978047376726</v>
       </c>
       <c r="K25">
-        <v>-5.5739541062734883E-2</v>
-      </c>
-      <c r="L25" s="2">
-        <v>0.1522620686275685</v>
+        <v>-0.05573950588579665</v>
+      </c>
+      <c r="L25">
+        <v>0.1522621468701011</v>
       </c>
       <c r="M25">
-        <v>0.1840377222761681</v>
+        <v>0.1840378173108739</v>
       </c>
       <c r="N25">
-        <v>0.19928739929864489</v>
+        <v>0.1992875803572606</v>
       </c>
       <c r="O25">
-        <v>0.1583043520776041</v>
+        <v>0.1583046262174217</v>
       </c>
       <c r="P25">
-        <v>0.10599419737483839</v>
+        <v>0.1059946052234794</v>
       </c>
       <c r="Q25">
-        <v>3.583851082120685E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>41</v>
+        <v>0.03583899420557392</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C26">
-        <v>-6.7730587431052106E-2</v>
+        <v>-0.06773060755351264</v>
       </c>
       <c r="D26">
-        <v>-0.13000919475617459</v>
+        <v>-0.1300091394240199</v>
       </c>
       <c r="E26">
-        <v>-0.14373763914635951</v>
+        <v>-0.1437376427920423</v>
       </c>
       <c r="F26">
-        <v>-8.5017289794046533E-2</v>
+        <v>-0.08501729810418611</v>
       </c>
       <c r="G26">
-        <v>-0.12343693877134181</v>
+        <v>-0.1234369159490532</v>
       </c>
       <c r="H26">
-        <v>-9.0197564755229651E-2</v>
+        <v>-0.09019751036837299</v>
       </c>
       <c r="I26">
-        <v>2.720956550588224E-2</v>
+        <v>0.0272096099951296</v>
       </c>
       <c r="J26">
-        <v>-4.8416731099570072E-2</v>
-      </c>
-      <c r="K26" s="2">
-        <v>9.5726021734760344E-2</v>
+        <v>-0.0484167068183264</v>
+      </c>
+      <c r="K26">
+        <v>0.09572617030841599</v>
       </c>
       <c r="L26">
-        <v>0.1840070224259234</v>
+        <v>0.1840073063570584</v>
       </c>
       <c r="M26">
-        <v>0.197873808564419</v>
+        <v>0.197873915667838</v>
       </c>
       <c r="N26">
-        <v>0.17485262065527651</v>
+        <v>0.1748528634871386</v>
       </c>
       <c r="O26">
-        <v>0.14239668000995101</v>
+        <v>0.1423970106060875</v>
       </c>
       <c r="P26">
-        <v>8.2395939595485981E-2</v>
+        <v>0.08239637861119734</v>
       </c>
       <c r="Q26">
-        <v>-4.4994142413409153E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>42</v>
+        <v>-0.004498863021495533</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C27">
-        <v>-6.9488828602768241E-2</v>
+        <v>-0.06948882766253504</v>
       </c>
       <c r="D27">
-        <v>-0.13147458805587309</v>
+        <v>-0.1314745109128995</v>
       </c>
       <c r="E27">
-        <v>-0.14454314046976841</v>
+        <v>-0.144543109128517</v>
       </c>
       <c r="F27">
-        <v>-7.9386756976424458E-2</v>
+        <v>-0.07938677694187986</v>
       </c>
       <c r="G27">
-        <v>-0.11887701638977929</v>
+        <v>-0.1188770017999381</v>
       </c>
       <c r="H27">
-        <v>-9.1450436018570933E-2</v>
+        <v>-0.09145039001077819</v>
       </c>
       <c r="I27">
-        <v>5.1256079097461481E-3</v>
+        <v>0.005125626665404275</v>
       </c>
       <c r="J27">
-        <v>-4.9073370827019631E-2</v>
+        <v>-0.04907335716394914</v>
       </c>
       <c r="K27">
-        <v>7.4895897482644289E-2</v>
-      </c>
-      <c r="L27" s="2">
-        <v>0.20921687259205271</v>
+        <v>0.07489607072883064</v>
+      </c>
+      <c r="L27">
+        <v>0.2092169153865491</v>
       </c>
       <c r="M27">
-        <v>0.25936439106711878</v>
+        <v>0.259364442339872</v>
       </c>
       <c r="N27">
-        <v>0.29167872878824558</v>
+        <v>0.2916788354510962</v>
       </c>
       <c r="O27">
-        <v>0.31017139390362991</v>
+        <v>0.3101715189052966</v>
       </c>
       <c r="P27">
-        <v>0.28348179650566302</v>
+        <v>0.2834819459695209</v>
       </c>
       <c r="Q27">
-        <v>0.27685180081345617</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>43</v>
+        <v>0.2768520257581435</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C28">
-        <v>-6.5067720490229602E-2</v>
+        <v>-0.06506772273698598</v>
       </c>
       <c r="D28">
-        <v>-0.1188209735978909</v>
+        <v>-0.1188209452786322</v>
       </c>
       <c r="E28">
-        <v>-0.1698063556419091</v>
+        <v>-0.1698063772809756</v>
       </c>
       <c r="F28">
-        <v>-0.12753098546736341</v>
+        <v>-0.1275309968171612</v>
       </c>
       <c r="G28">
-        <v>-0.108638314943881</v>
+        <v>-0.1086392886384782</v>
       </c>
       <c r="H28">
-        <v>-9.0487052984105643E-2</v>
+        <v>-0.09048712111094462</v>
       </c>
       <c r="I28">
-        <v>-0.15601152801020629</v>
+        <v>-0.156011527161265</v>
       </c>
       <c r="J28">
-        <v>-0.13210531162208181</v>
+        <v>-0.132105293514663</v>
       </c>
       <c r="K28">
-        <v>-6.8297247425719465E-2</v>
-      </c>
-      <c r="L28" s="2">
-        <v>0.15705516650328491</v>
+        <v>-0.06829723204117764</v>
+      </c>
+      <c r="L28">
+        <v>0.1570552099192431</v>
       </c>
       <c r="M28">
-        <v>0.2026701550898124</v>
+        <v>0.202670204316038</v>
       </c>
       <c r="N28">
-        <v>0.23226084738517949</v>
+        <v>0.2322608966509875</v>
       </c>
       <c r="O28">
-        <v>0.24202019468594391</v>
+        <v>0.2420202934451105</v>
       </c>
       <c r="P28">
-        <v>0.24571166286576859</v>
+        <v>0.2457117707006031</v>
       </c>
       <c r="Q28">
-        <v>0.23718763369396001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>44</v>
+        <v>0.2371877638721149</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C29">
-        <v>-6.8512567829549079E-2</v>
+        <v>-0.06851256674180652</v>
       </c>
       <c r="D29">
-        <v>-0.1257885359990259</v>
+        <v>-0.1257884731091098</v>
       </c>
       <c r="E29">
-        <v>-0.18256838385234911</v>
+        <v>-0.1825684112211571</v>
       </c>
       <c r="F29">
-        <v>-0.13982442189672101</v>
+        <v>-0.1398244600215701</v>
       </c>
       <c r="G29">
-        <v>-0.1163912176281334</v>
+        <v>-0.116391202827967</v>
       </c>
       <c r="H29">
-        <v>-9.4802083974037527E-2</v>
+        <v>-0.09480208235284081</v>
       </c>
       <c r="I29">
-        <v>-0.16031497256999511</v>
+        <v>-0.1603149655403011</v>
       </c>
       <c r="J29">
-        <v>-0.13414904264095051</v>
+        <v>-0.1341490233395761</v>
       </c>
       <c r="K29">
-        <v>-7.0586245094377387E-2</v>
-      </c>
-      <c r="L29" s="2">
-        <v>0.141956344739886</v>
+        <v>-0.07058629273538317</v>
+      </c>
+      <c r="L29">
+        <v>0.1419563907498062</v>
       </c>
       <c r="M29">
-        <v>0.19518619899985559</v>
+        <v>0.1951862661038739</v>
       </c>
       <c r="N29">
-        <v>0.23729070239233971</v>
+        <v>0.2372907536875827</v>
       </c>
       <c r="O29">
-        <v>0.25098601316714969</v>
+        <v>0.2509860572088142</v>
       </c>
       <c r="P29">
-        <v>0.26057631671746978</v>
+        <v>0.2605764238144377</v>
       </c>
       <c r="Q29">
-        <v>0.27204286004660078</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>45</v>
+        <v>0.2720429882015462</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C30">
-        <v>-7.1212799957591916E-2</v>
+        <v>-0.07121280021655874</v>
       </c>
       <c r="D30">
-        <v>-0.127368887631229</v>
+        <v>-0.1273688451850707</v>
       </c>
       <c r="E30">
-        <v>-0.1747719583256257</v>
+        <v>-0.1747719751125089</v>
       </c>
       <c r="F30">
-        <v>-0.13326718222898021</v>
+        <v>-0.1332671858255354</v>
       </c>
       <c r="G30">
-        <v>-0.1115701096274733</v>
+        <v>-0.1115700854663973</v>
       </c>
       <c r="H30">
-        <v>-9.292343232174699E-2</v>
+        <v>-0.09292351491176595</v>
       </c>
       <c r="I30">
-        <v>-0.1530618203678962</v>
+        <v>-0.1530617958460734</v>
       </c>
       <c r="J30">
-        <v>-0.1207557500223258</v>
+        <v>-0.120755785467166</v>
       </c>
       <c r="K30">
-        <v>-7.0239183398508265E-2</v>
-      </c>
-      <c r="L30" s="2">
-        <v>0.14086259189315189</v>
+        <v>-0.0702392118802269</v>
+      </c>
+      <c r="L30">
+        <v>0.1408626469288831</v>
       </c>
       <c r="M30">
-        <v>0.1965092148556713</v>
+        <v>0.1965092735682412</v>
       </c>
       <c r="N30">
-        <v>0.2343706584232918</v>
+        <v>0.2343707111586116</v>
       </c>
       <c r="O30">
-        <v>0.25478579331619838</v>
+        <v>0.2547858823660602</v>
       </c>
       <c r="P30">
-        <v>0.27248032003499911</v>
+        <v>0.2724804039788679</v>
       </c>
       <c r="Q30">
-        <v>0.28322408082184197</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>46</v>
+        <v>0.2832242040261927</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C31">
-        <v>-6.3516947428013171E-2</v>
+        <v>-0.06351695764024731</v>
       </c>
       <c r="D31">
-        <v>-0.1131046384313398</v>
+        <v>-0.1131045303685413</v>
       </c>
       <c r="E31">
-        <v>-0.16805298918487629</v>
+        <v>-0.1680529937648193</v>
       </c>
       <c r="F31">
-        <v>-0.1243617123525932</v>
+        <v>-0.1243617285314717</v>
       </c>
       <c r="G31">
-        <v>-0.10607497413656999</v>
+        <v>-0.1060749530096426</v>
       </c>
       <c r="H31">
-        <v>-8.7629763293037705E-2</v>
+        <v>-0.08762974464494673</v>
       </c>
       <c r="I31">
-        <v>-0.1525507869246332</v>
+        <v>-0.1525507755618765</v>
       </c>
       <c r="J31">
-        <v>-0.14131360695189729</v>
+        <v>-0.1413135988872946</v>
       </c>
       <c r="K31">
-        <v>-8.9935786277619445E-2</v>
-      </c>
-      <c r="L31" s="2">
-        <v>0.1149308881575259</v>
+        <v>-0.08993567765506143</v>
+      </c>
+      <c r="L31">
+        <v>0.1149309350348776</v>
       </c>
       <c r="M31">
-        <v>0.17204870321328261</v>
+        <v>0.1720487868730037</v>
       </c>
       <c r="N31">
-        <v>0.20397271852992591</v>
+        <v>0.2039727819913283</v>
       </c>
       <c r="O31">
-        <v>0.23840462669948359</v>
+        <v>0.2384046710646423</v>
       </c>
       <c r="P31">
-        <v>0.25183759857675941</v>
+        <v>0.2518376519655145</v>
       </c>
       <c r="Q31">
-        <v>0.27269776863783779</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>47</v>
+        <v>0.2726978522990322</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C32">
-        <v>-6.4725790130664096E-2</v>
+        <v>-0.06472579497386811</v>
       </c>
       <c r="D32">
-        <v>-0.12173632301152219</v>
+        <v>-0.1217362891312413</v>
       </c>
       <c r="E32">
-        <v>-0.17762849941848369</v>
+        <v>-0.1776285115992853</v>
       </c>
       <c r="F32">
-        <v>-0.13347995301150231</v>
+        <v>-0.1334798729374318</v>
       </c>
       <c r="G32">
-        <v>-0.1086701185987885</v>
+        <v>-0.1086700715360825</v>
       </c>
       <c r="H32">
-        <v>-8.4833057056379751E-2</v>
+        <v>-0.08483298077575684</v>
       </c>
       <c r="I32">
-        <v>-0.1478442053649798</v>
+        <v>-0.1478441921947571</v>
       </c>
       <c r="J32">
-        <v>-0.1150327636611633</v>
+        <v>-0.1150327395396779</v>
       </c>
       <c r="K32">
-        <v>-5.1093589707120683E-2</v>
-      </c>
-      <c r="L32" s="2">
-        <v>0.17191473748712471</v>
+        <v>-0.05109357199895553</v>
+      </c>
+      <c r="L32">
+        <v>0.1719148042557848</v>
       </c>
       <c r="M32">
-        <v>0.21303965636470171</v>
+        <v>0.2130397245209669</v>
       </c>
       <c r="N32">
-        <v>0.23740773559422501</v>
+        <v>0.2374078244814244</v>
       </c>
       <c r="O32">
-        <v>0.23771189200381851</v>
+        <v>0.2377119838660482</v>
       </c>
       <c r="P32">
-        <v>0.22433759205169479</v>
+        <v>0.2243377147110457</v>
       </c>
       <c r="Q32">
-        <v>0.21161783003019849</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>48</v>
+        <v>0.2116180148819103</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C33">
-        <v>-7.0702132126642461E-2</v>
+        <v>-0.07070212893911951</v>
       </c>
       <c r="D33">
-        <v>-0.1293841519702939</v>
+        <v>-0.1293840979238772</v>
       </c>
       <c r="E33">
-        <v>-0.1833990485307242</v>
+        <v>-0.1833988497065487</v>
       </c>
       <c r="F33">
-        <v>-0.14132731539492949</v>
+        <v>-0.1413273152588899</v>
       </c>
       <c r="G33">
-        <v>-0.1153777795725576</v>
+        <v>-0.1153777571636728</v>
       </c>
       <c r="H33">
-        <v>-9.9347513074941329E-2</v>
+        <v>-0.09934750932307237</v>
       </c>
       <c r="I33">
-        <v>-0.16348185023935899</v>
+        <v>-0.1634818203509821</v>
       </c>
       <c r="J33">
-        <v>-0.13226190133855709</v>
+        <v>-0.1322618978431151</v>
       </c>
       <c r="K33">
-        <v>-7.071816985137297E-2</v>
-      </c>
-      <c r="L33" s="2">
-        <v>0.1397640244657854</v>
+        <v>-0.07071815160565485</v>
+      </c>
+      <c r="L33">
+        <v>0.1397640873780094</v>
       </c>
       <c r="M33">
-        <v>0.18996911419725859</v>
+        <v>0.1899691887481041</v>
       </c>
       <c r="N33">
-        <v>0.2185019880724802</v>
+        <v>0.2185020878291289</v>
       </c>
       <c r="O33">
-        <v>0.2269616571571795</v>
+        <v>0.2269617581871511</v>
       </c>
       <c r="P33">
-        <v>0.21931412093480751</v>
+        <v>0.2193142706658937</v>
       </c>
       <c r="Q33">
-        <v>0.2074891728881284</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>49</v>
+        <v>0.2074893471809246</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C34">
-        <v>-6.8855211762843649E-2</v>
+        <v>-0.06885523098938953</v>
       </c>
       <c r="D34">
-        <v>-0.12949919202117821</v>
+        <v>-0.1294991033805815</v>
       </c>
       <c r="E34">
-        <v>-0.1847754532629389</v>
+        <v>-0.184775469967379</v>
       </c>
       <c r="F34">
-        <v>-0.13718487751185779</v>
+        <v>-0.1371848701107108</v>
       </c>
       <c r="G34">
-        <v>-0.1176480392282656</v>
+        <v>-0.1176479901431906</v>
       </c>
       <c r="H34">
-        <v>-9.7632529775008234E-2</v>
+        <v>-0.09763252645001226</v>
       </c>
       <c r="I34">
-        <v>-0.16788320882913971</v>
+        <v>-0.1678832036474063</v>
       </c>
       <c r="J34">
-        <v>-0.12890380732192139</v>
+        <v>-0.1289038127727916</v>
       </c>
       <c r="K34">
-        <v>-7.0073649564574264E-2</v>
-      </c>
-      <c r="L34" s="2">
-        <v>0.1219296448991528</v>
+        <v>-0.07007364865989503</v>
+      </c>
+      <c r="L34">
+        <v>0.1219296899193601</v>
       </c>
       <c r="M34">
-        <v>0.17893416701723031</v>
+        <v>0.1789342195718091</v>
       </c>
       <c r="N34">
-        <v>0.20899544364395051</v>
+        <v>0.2089955259089124</v>
       </c>
       <c r="O34">
-        <v>0.22848280408630861</v>
+        <v>0.2284828187512663</v>
       </c>
       <c r="P34">
-        <v>0.22885553074563869</v>
+        <v>0.2288556409538918</v>
       </c>
       <c r="Q34">
-        <v>0.21913537360863669</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>50</v>
+        <v>0.2191355097052953</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C35">
-        <v>-6.8813963016539109E-2</v>
+        <v>-0.06881397597238717</v>
       </c>
       <c r="D35">
-        <v>-0.1202195254136415</v>
+        <v>-0.1202194703877492</v>
       </c>
       <c r="E35">
-        <v>-0.17328306132531049</v>
+        <v>-0.1732830836997162</v>
       </c>
       <c r="F35">
-        <v>-0.13131740724488791</v>
+        <v>-0.1313173575663137</v>
       </c>
       <c r="G35">
-        <v>-0.1102599711451672</v>
+        <v>-0.1102598051798082</v>
       </c>
       <c r="H35">
-        <v>-9.2510106561050603E-2</v>
+        <v>-0.0925101023714912</v>
       </c>
       <c r="I35">
-        <v>-0.16550434432355091</v>
+        <v>-0.1655043203651407</v>
       </c>
       <c r="J35">
-        <v>-0.14002536728150411</v>
+        <v>-0.140025394847188</v>
       </c>
       <c r="K35">
-        <v>-7.8895188556222906E-2</v>
-      </c>
-      <c r="L35" s="2">
-        <v>0.13714318091539299</v>
+        <v>-0.07889518097682358</v>
+      </c>
+      <c r="L35">
+        <v>0.1371432190633085</v>
       </c>
       <c r="M35">
-        <v>0.18207000176330021</v>
+        <v>0.1820700535580482</v>
       </c>
       <c r="N35">
-        <v>0.2172169501020384</v>
+        <v>0.2172170097194879</v>
       </c>
       <c r="O35">
-        <v>0.2289306238327192</v>
+        <v>0.2289306853491068</v>
       </c>
       <c r="P35">
-        <v>0.2275984616563772</v>
+        <v>0.2275985656539069</v>
       </c>
       <c r="Q35">
-        <v>0.2286712040521108</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>51</v>
+        <v>0.2286713472148749</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C36">
-        <v>-6.9401051963059707E-2</v>
+        <v>-0.06940105358735792</v>
       </c>
       <c r="D36">
-        <v>-0.12739609563542539</v>
+        <v>-0.1273960629143482</v>
       </c>
       <c r="E36">
-        <v>-0.1752323047956949</v>
+        <v>-0.1752323049441195</v>
       </c>
       <c r="F36">
-        <v>-0.1342760171207408</v>
+        <v>-0.1342759720939638</v>
       </c>
       <c r="G36">
-        <v>-0.1135693756968526</v>
+        <v>-0.1135691911677978</v>
       </c>
       <c r="H36">
-        <v>-9.5271626867414583E-2</v>
+        <v>-0.09527146858529338</v>
       </c>
       <c r="I36">
-        <v>-0.15573047551935421</v>
+        <v>-0.1557304830144439</v>
       </c>
       <c r="J36">
-        <v>-0.12869790045444771</v>
+        <v>-0.1286978948204666</v>
       </c>
       <c r="K36">
-        <v>-7.8868720799060724E-2</v>
-      </c>
-      <c r="L36" s="2">
-        <v>0.10347042300664221</v>
+        <v>-0.07886870281582366</v>
+      </c>
+      <c r="L36">
+        <v>0.1034704743217286</v>
       </c>
       <c r="M36">
-        <v>0.179207113188038</v>
+        <v>0.179207169495111</v>
       </c>
       <c r="N36">
-        <v>0.2036573088278506</v>
+        <v>0.2036573730606822</v>
       </c>
       <c r="O36">
-        <v>0.24091566928671809</v>
+        <v>0.2409157162720221</v>
       </c>
       <c r="P36">
-        <v>0.25269685642156631</v>
+        <v>0.2526969218172567</v>
       </c>
       <c r="Q36">
-        <v>0.28123392102254019</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>52</v>
+        <v>0.281234011888341</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C37">
-        <v>-0.1175539354686162</v>
+        <v>-0.1175539095735951</v>
       </c>
       <c r="D37">
-        <v>-0.19408758984237401</v>
+        <v>-0.1940876073310111</v>
       </c>
       <c r="E37">
-        <v>-0.12001242668167129</v>
+        <v>-0.1200124335152508</v>
       </c>
       <c r="F37">
-        <v>-3.2034150828240723E-2</v>
+        <v>-0.03203418431686669</v>
       </c>
       <c r="G37">
-        <v>-9.9366406258134893E-2</v>
+        <v>-0.09936639079897334</v>
       </c>
       <c r="H37">
-        <v>-4.2715767443932733E-2</v>
+        <v>-0.04271570376597202</v>
       </c>
       <c r="I37">
-        <v>4.7579825462109079E-2</v>
+        <v>0.04758003053748655</v>
       </c>
       <c r="J37">
-        <v>8.4142327349591789E-2</v>
+        <v>0.08414256884652475</v>
       </c>
       <c r="K37">
-        <v>7.8542428458030958E-2</v>
+        <v>0.07854269190929589</v>
       </c>
       <c r="L37">
-        <v>8.4728020576492577E-2</v>
+        <v>0.08472836487021627</v>
       </c>
       <c r="M37">
-        <v>7.4420679216229857E-2</v>
+        <v>0.07442101335663723</v>
       </c>
       <c r="N37">
-        <v>3.1951043030654859E-2</v>
+        <v>0.03195149684268409</v>
       </c>
       <c r="O37">
-        <v>5.471005829846378E-2</v>
+        <v>0.05471071229602212</v>
       </c>
       <c r="P37">
-        <v>5.5359573737743847E-2</v>
+        <v>0.05536047785669723</v>
       </c>
       <c r="Q37">
-        <v>5.630439708252076E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>53</v>
+        <v>0.05630544361610515</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C38">
-        <v>-9.0468185548435304E-2</v>
+        <v>-0.09046815599182326</v>
       </c>
       <c r="D38">
-        <v>-0.17331253967012181</v>
+        <v>-0.1733125535449494</v>
       </c>
       <c r="E38">
-        <v>-0.1434707399930758</v>
+        <v>-0.1434709105018855</v>
       </c>
       <c r="F38">
-        <v>5.4753943733241196E-3</v>
+        <v>0.00547549331538543</v>
       </c>
       <c r="G38">
-        <v>3.017413303385446E-2</v>
-      </c>
-      <c r="H38" s="2">
-        <v>0.15316216711699379</v>
+        <v>0.03017415165306785</v>
+      </c>
+      <c r="H38">
+        <v>0.1531621720471866</v>
       </c>
       <c r="I38">
-        <v>0.27572866078807551</v>
+        <v>0.2757286999703113</v>
       </c>
       <c r="J38">
-        <v>0.27391849807032942</v>
+        <v>0.2739185951309173</v>
       </c>
       <c r="K38">
-        <v>0.2360526929203787</v>
+        <v>0.2360527934528286</v>
       </c>
       <c r="L38">
-        <v>0.19787789111839951</v>
+        <v>0.1978780721824886</v>
       </c>
       <c r="M38">
-        <v>0.19181526409789471</v>
+        <v>0.1918154961786713</v>
       </c>
       <c r="N38">
-        <v>0.18133114871741199</v>
+        <v>0.1813314061754044</v>
       </c>
       <c r="O38">
-        <v>0.18391515336324091</v>
+        <v>0.1839154347705579</v>
       </c>
       <c r="P38">
-        <v>0.1986089856150571</v>
+        <v>0.1986092004812028</v>
       </c>
       <c r="Q38">
-        <v>0.20695635302227949</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>54</v>
+        <v>0.2069566118420303</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C39">
-        <v>-8.5336246490704468E-2</v>
+        <v>-0.08533622394841402</v>
       </c>
       <c r="D39">
-        <v>-0.1589941323337766</v>
+        <v>-0.1589941244858831</v>
       </c>
       <c r="E39">
-        <v>-0.1192277591023872</v>
+        <v>-0.1192277331901163</v>
       </c>
       <c r="F39">
-        <v>8.2234166630224398E-3</v>
+        <v>0.008223520202152269</v>
       </c>
       <c r="G39">
-        <v>1.080875580467687E-2</v>
-      </c>
-      <c r="H39" s="2">
-        <v>0.1203137534243368</v>
+        <v>0.0108087574116707</v>
+      </c>
+      <c r="H39">
+        <v>0.1203137444787629</v>
       </c>
       <c r="I39">
-        <v>0.2449264373844148</v>
+        <v>0.2449264551065707</v>
       </c>
       <c r="J39">
-        <v>0.23673034667195941</v>
+        <v>0.236730398837845</v>
       </c>
       <c r="K39">
-        <v>0.24509777079502751</v>
+        <v>0.2450978567971423</v>
       </c>
       <c r="L39">
-        <v>0.2379521074198018</v>
+        <v>0.237952241705632</v>
       </c>
       <c r="M39">
-        <v>0.21896378850475831</v>
+        <v>0.2189639474951441</v>
       </c>
       <c r="N39">
-        <v>0.23996265588138579</v>
+        <v>0.2399630212228847</v>
       </c>
       <c r="O39">
-        <v>0.22353311109204599</v>
+        <v>0.2235343262553569</v>
       </c>
       <c r="P39">
-        <v>0.20998559843243919</v>
+        <v>0.2099858689880199</v>
       </c>
       <c r="Q39">
-        <v>0.21574131726647011</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>55</v>
+        <v>0.2157416510021851</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C40">
-        <v>-0.10616119317134209</v>
+        <v>-0.1061611669208593</v>
       </c>
       <c r="D40">
-        <v>-7.7592299444609325E-2</v>
+        <v>-0.07759225903971138</v>
       </c>
       <c r="E40">
-        <v>-7.5792489616482615E-4</v>
+        <v>-0.0007579417136614934</v>
       </c>
       <c r="F40">
-        <v>-2.5390698579601391E-2</v>
+        <v>-0.02539062771886768</v>
       </c>
       <c r="G40">
-        <v>9.6014915333048262E-2</v>
+        <v>0.09601491332523047</v>
       </c>
       <c r="H40">
-        <v>0.15673446745269529</v>
-      </c>
-      <c r="I40" s="2">
-        <v>0.1569208148044462</v>
+        <v>0.1567345255319861</v>
+      </c>
+      <c r="I40">
+        <v>0.1569209503130176</v>
       </c>
       <c r="J40">
-        <v>0.11724822553668381</v>
+        <v>0.1172484614554646</v>
       </c>
       <c r="K40">
-        <v>0.1192720057202226</v>
+        <v>0.1192722716181247</v>
       </c>
       <c r="L40">
-        <v>0.15506423597339239</v>
+        <v>0.1550645321691183</v>
       </c>
       <c r="M40">
-        <v>0.14787436812908961</v>
+        <v>0.1478746666063541</v>
       </c>
       <c r="N40">
-        <v>0.16621807005252531</v>
+        <v>0.16621842155277</v>
       </c>
       <c r="O40">
-        <v>0.14929871768945371</v>
+        <v>0.1492992246845898</v>
       </c>
       <c r="P40">
-        <v>0.1196870716000647</v>
+        <v>0.119687690135812</v>
       </c>
       <c r="Q40">
-        <v>5.5571810564084632E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>56</v>
+        <v>0.0555726519907416</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C41">
-        <v>-0.1164723144882223</v>
+        <v>-0.1164723555043632</v>
       </c>
       <c r="D41">
-        <v>-0.26597461324775701</v>
+        <v>-0.265974585832102</v>
       </c>
       <c r="E41">
-        <v>-0.17348880203750219</v>
+        <v>-0.1734888127094565</v>
       </c>
       <c r="F41">
-        <v>-0.17069972490826771</v>
+        <v>-0.1706997307168271</v>
       </c>
       <c r="G41">
-        <v>-8.893233550147453E-2</v>
+        <v>-0.08893233400523186</v>
       </c>
       <c r="H41">
-        <v>-7.2017027146971072E-2</v>
+        <v>-0.07201705222082355</v>
       </c>
       <c r="I41">
-        <v>-4.3450693824968752E-2</v>
+        <v>-0.04345065548551879</v>
       </c>
       <c r="J41">
-        <v>3.8976088728526221E-3</v>
+        <v>0.003897659023151337</v>
       </c>
       <c r="K41">
-        <v>-3.4162224695663802E-2</v>
+        <v>-0.0341621451380597</v>
       </c>
       <c r="L41">
-        <v>-6.3573828818924275E-2</v>
+        <v>-0.06357373383423477</v>
       </c>
       <c r="M41">
-        <v>-6.5202853364924249E-2</v>
+        <v>-0.06520270261747099</v>
       </c>
       <c r="N41">
-        <v>-8.6423706699215619E-2</v>
+        <v>-0.08642349161139783</v>
       </c>
       <c r="O41">
-        <v>-0.1387459552174676</v>
+        <v>-0.1387457073765568</v>
       </c>
       <c r="P41">
-        <v>-0.1456562348845773</v>
+        <v>-0.1456559595573281</v>
       </c>
       <c r="Q41">
-        <v>-0.15975210524660749</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>57</v>
+        <v>-0.1597517953661197</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C42">
-        <v>-2.4079129103167521E-2</v>
+        <v>-0.02407913786094402</v>
       </c>
       <c r="D42">
-        <v>-0.31885267084009772</v>
+        <v>-0.3188527565154617</v>
       </c>
       <c r="E42">
-        <v>-0.19611721182558511</v>
+        <v>-0.1961172389179193</v>
       </c>
       <c r="F42">
-        <v>4.7060746188968577E-2</v>
+        <v>0.04706071661321934</v>
       </c>
       <c r="G42">
-        <v>0.1229690818531753</v>
-      </c>
-      <c r="H42" s="2">
-        <v>0.172588940126745</v>
+        <v>0.1229690483236442</v>
+      </c>
+      <c r="H42">
+        <v>0.1725889730581215</v>
       </c>
       <c r="I42">
-        <v>0.25790387732600972</v>
+        <v>0.257903891264724</v>
       </c>
       <c r="J42">
-        <v>0.26902268604335328</v>
+        <v>0.2690227186396865</v>
       </c>
       <c r="K42">
-        <v>0.2468139738700367</v>
+        <v>0.2468140412827627</v>
       </c>
       <c r="L42">
-        <v>0.26911413612907692</v>
+        <v>0.2691141922424644</v>
       </c>
       <c r="M42">
-        <v>0.26596213009884812</v>
+        <v>0.2659621447185102</v>
       </c>
       <c r="N42">
-        <v>0.24879965921958169</v>
+        <v>0.2487998221781705</v>
       </c>
       <c r="O42">
-        <v>0.24120905378712901</v>
+        <v>0.2412092559015532</v>
       </c>
       <c r="P42">
-        <v>0.24648529336658409</v>
+        <v>0.246485532124656</v>
       </c>
       <c r="Q42">
-        <v>0.2291626243901593</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>58</v>
+        <v>0.2291628933744766</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>-1.8778932657874229E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C43">
-        <v>-6.9897652745686184E-2</v>
+        <v>-0.06989770134927845</v>
       </c>
       <c r="D43">
-        <v>-0.11434416288305101</v>
+        <v>-0.1143441706460183</v>
       </c>
       <c r="E43">
-        <v>-1.050785869509642E-2</v>
+        <v>-0.01050780370451789</v>
       </c>
       <c r="F43">
-        <v>2.7003765047599292E-2</v>
-      </c>
-      <c r="G43" s="2">
-        <v>0.17856656190608899</v>
+        <v>0.02700375579164554</v>
+      </c>
+      <c r="G43">
+        <v>0.1785665356809124</v>
       </c>
       <c r="H43">
-        <v>0.23180627375430499</v>
+        <v>0.231806265521214</v>
       </c>
       <c r="I43">
-        <v>0.26251075681529612</v>
+        <v>0.2625107537809444</v>
       </c>
       <c r="J43">
-        <v>0.25470903299200931</v>
+        <v>0.254709023079752</v>
       </c>
       <c r="K43">
-        <v>0.2205984990880073</v>
+        <v>0.2205985475231721</v>
       </c>
       <c r="L43">
-        <v>0.26179585040142411</v>
+        <v>0.2617958902312684</v>
       </c>
       <c r="M43">
-        <v>0.26491160214751108</v>
+        <v>0.2649116770888011</v>
       </c>
       <c r="N43">
-        <v>0.26635803722964457</v>
+        <v>0.2663581427614504</v>
       </c>
       <c r="O43">
-        <v>0.25131626953869313</v>
+        <v>0.2513163995467447</v>
       </c>
       <c r="P43">
-        <v>0.23205392819497389</v>
+        <v>0.2320540876034953</v>
       </c>
       <c r="Q43">
-        <v>0.21436188250370569</v>
+        <v>0.2143619769360944</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:Q43">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>